--- a/Beyomo_Changes_List.xlsx
+++ b/Beyomo_Changes_List.xlsx
@@ -1221,7 +1221,653 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">67</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin Dashboard</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Service offer pricing - Add, edit or clear an offer price, with the original price and calculated discount percentage displayed in service lists and cards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin Dashboard</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Offer prices in admin bookings - New bookings and added catalog services use valid offer prices; booking details show the original price and discount alongside the charged amount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin Dashboard</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Separate website service description - Admin can save a website-specific description separately from the regular service description.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin Dashboard</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sharper service and banner previews - Image previews are capped at their required upload dimensions to avoid blur caused by stretching smaller images.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer App</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cart shortcut in bottom navigation - Open checkout directly from the Cart button, with a badge showing the number of selected items.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer App</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Services, combos and packages in one cart - Checkout handles multiple packages and individual services together, with independent package quantities and correctly calculated extras.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">73</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer App</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Add More Services from checkout - Returns to Home so customers can add services, combos or packages and come back with their selections retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer App</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Checkout state reset for a different package - Reopening checkout with another package refreshes its services, quantities and offer state instead of retaining the previous package selections.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">75</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer App</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Service offer prices throughout the app - Home cards, service lists, cart, checkout and booking details show the discounted price, crossed-out original price and percentage off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">76</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer App</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removed service offers refresh automatically - Service screens and checkout recheck offers, restore normal prices and update cart totals with an in-app notice when an offer is no longer available; prices are checked again before payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer App</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Free-service offer eligibility rechecked - Removing qualifying paid services clears an ineligible free item; eligibility is checked again before booking submission.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer App</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Download and view booking invoices - Generates a PDF invoice from booking data, saves it on the device and provides a View Invoice action with clear success or failure feedback.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer App</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Share booking details - Opens the device share sheet with the booking reference, status, schedule, service count and total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer App</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Booking cancellation and reschedule controls - Cancel uses an in-app confirmation; reschedule is offered only for pending or confirmed bookings, and rescheduled bookings have a visible badge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer App</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Add-service confirmation on booking details - Shows an in-app success message with the number of services added and the updated booking total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer App</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Minimum booking amount enforced - Checkout requires a Rs. 500 subtotal and shows how much more must be added before booking can continue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">83</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer App</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Booking-time validation - Checks the advance booking buffer and service hours of 8 AM to 8 PM; the default slot moves to next-day opening when the advance buffer passes closing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer App</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Checkout address restricted to the selected city - Only a matching-city default address is selected; switching city clears an address belonging to another city.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">85</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer App</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Service quantity limit in checkout - Service quantities are capped at five in checkout controls.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer App</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Most Booked service details - Home cards open a service details sheet; customers can dismiss it by swiping down on the handle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer App</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Home navigation and search improvements - View All Services is available whenever categories exist, and search includes categories, services, packages and offers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer App</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Missing-image placeholders on Home - Most Booked services and package/combo banners display a No image found placeholder when no image is supplied.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer App</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package and combo layout improvements - Loading indicators are centred and Book Now aligns at the bottom of combo cards with different service counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer App</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer notifications fixed - The notification list and unread count now read the API response correctly instead of showing an empty list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer App</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">My Reviews crash fixed - Review cards read nested service and partner details correctly and display their names and images.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer App</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Address form keyboard handling on iOS - The address form adjusts and scrolls while typing so the keyboard does not cover the fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partner App</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arrival, OTP verification and service start flow - Swipe Reached to Customer Location to open the checklist and customer OTP prompt; verifying the code unlocks a separate Start Service swipe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partner App</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reopen customer OTP verification - If the OTP sheet is dismissed, Verify Customer OTP opens it again; the sheet adjusts for the keyboard and can be closed by tapping outside.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">95</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partner App</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">iOS swipe gesture fixes - Confirmation swipes work with iOS navigation gestures; the embedded arrival swipe temporarily pauses parent scrolling while dragging.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partner App</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Add combos and packages from the checklist - Separate tabs allow fixed combos and flexible packages to be added, including choosing the required number of services for a flexible package.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">97</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partner App</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove checklist services at quantity one - The minus control becomes a delete icon when only one item remains; the catalog selection can also be cleared at quantity one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partner App</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Offer pricing on partner services - Catalog selections and checklist/active-job services show valid offer prices, original prices and discount percentages, with totals calculated from the offer price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partner App</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removed offers on partner-added services - Checklist and active-job screens recheck offers and restore normal prices for affected partner-added services, update booking totals and notify the partner before continuing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partner App</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Service catalog retry in checklist - Loading errors show a clear message and Retry action instead of leaving an empty service picker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partner App</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removed-service labels in job details - Services removed from a job display a Removed badge alongside the existing Added label for partner additions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partner App</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partner login and approval navigation reset - Successful login and entry after approval clear the previous login/OTP/account-status navigation history.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partner App</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partner login OTP keyboard handling - The OTP screen scrolls and adjusts to the keyboard so verification controls remain accessible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">104</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partner App</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Availability toggle refresh race fixed - Dashboard polling respects an in-progress availability change, and foreground handling reads the latest online state.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C67"/>
+  <autoFilter ref="A1:C105"/>
 </worksheet>
 </file>